--- a/week-01/Ex4A_GTrends.xlsx
+++ b/week-01/Ex4A_GTrends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luise\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AA48029-60E4-4F80-B7BB-5BC784CD556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{161BDF74-6F1D-49FF-BAC6-1B500DF1D2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="7730" xr2:uid="{F2D51FF9-8D78-491B-A923-8BC310781854}"/>
+    <workbookView xWindow="10" yWindow="3920" windowWidth="19200" windowHeight="11010" xr2:uid="{3F803DB3-4EA7-46F6-AE33-96C98E33509F}"/>
   </bookViews>
   <sheets>
     <sheet name="GTrends_milkshake_hamburger_202" sheetId="1" r:id="rId1"/>
@@ -20,21 +20,174 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Category: All categories</t>
   </si>
   <si>
-    <t>Week</t>
-  </si>
-  <si>
-    <t>Milkshake: (United States)</t>
-  </si>
-  <si>
-    <t>Hamburger: (United States)</t>
-  </si>
-  <si>
-    <t>Breakup: (United States)</t>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Milkshake: (2/1/24 - 2/28/25)</t>
+  </si>
+  <si>
+    <t>Breakup: (2/1/24 - 2/28/25)</t>
+  </si>
+  <si>
+    <t>Hamburger: (2/1/24 - 2/28/25)</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>District of Columbia</t>
   </si>
 </sst>
 </file>
@@ -520,7 +673,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -895,15 +1048,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACFECB69-27D8-4EE1-90B1-D22E21ED6D8D}">
-  <dimension ref="A1:D60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2568FC69-474F-4A0E-BC4E-D3E6E5AE3952}">
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7265625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -925,801 +1072,717 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>45319</v>
-      </c>
-      <c r="B4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="C4">
-        <v>68</v>
-      </c>
-      <c r="D4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>45326</v>
-      </c>
-      <c r="B5">
+      <c r="B22" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>25</v>
       </c>
-      <c r="C5">
-        <v>69</v>
-      </c>
-      <c r="D5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>45333</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>65</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>45340</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>70</v>
-      </c>
-      <c r="D7">
+      <c r="B24" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>45347</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>66</v>
-      </c>
-      <c r="D8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>45354</v>
-      </c>
-      <c r="B9">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>68</v>
-      </c>
-      <c r="D9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>45361</v>
-      </c>
-      <c r="B10">
-        <v>26</v>
-      </c>
-      <c r="C10">
-        <v>68</v>
-      </c>
-      <c r="D10">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>45368</v>
-      </c>
-      <c r="B11">
-        <v>25</v>
-      </c>
-      <c r="C11">
-        <v>62</v>
-      </c>
-      <c r="D11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>45375</v>
-      </c>
-      <c r="B12">
-        <v>23</v>
-      </c>
-      <c r="C12">
-        <v>66</v>
-      </c>
-      <c r="D12">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>45382</v>
-      </c>
-      <c r="B13">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>62</v>
-      </c>
-      <c r="D13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>45389</v>
-      </c>
-      <c r="B14">
-        <v>21</v>
-      </c>
-      <c r="C14">
-        <v>67</v>
-      </c>
-      <c r="D14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>45396</v>
-      </c>
-      <c r="B15">
-        <v>22</v>
-      </c>
-      <c r="C15">
-        <v>70</v>
-      </c>
-      <c r="D15">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>45403</v>
-      </c>
-      <c r="B16">
-        <v>22</v>
-      </c>
-      <c r="C16">
-        <v>68</v>
-      </c>
-      <c r="D16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>45410</v>
-      </c>
-      <c r="B17">
-        <v>21</v>
-      </c>
-      <c r="C17">
-        <v>67</v>
-      </c>
-      <c r="D17">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>45417</v>
-      </c>
-      <c r="B18">
-        <v>21</v>
-      </c>
-      <c r="C18">
-        <v>65</v>
-      </c>
-      <c r="D18">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>45424</v>
-      </c>
-      <c r="B19">
-        <v>22</v>
-      </c>
-      <c r="C19">
-        <v>69</v>
-      </c>
-      <c r="D19">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>45431</v>
-      </c>
-      <c r="B20">
-        <v>21</v>
-      </c>
-      <c r="C20">
-        <v>73</v>
-      </c>
-      <c r="D20">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>45438</v>
-      </c>
-      <c r="B21">
-        <v>22</v>
-      </c>
-      <c r="C21">
-        <v>100</v>
-      </c>
-      <c r="D21">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>45445</v>
-      </c>
-      <c r="B22">
-        <v>23</v>
-      </c>
-      <c r="C22">
-        <v>70</v>
-      </c>
-      <c r="D22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>45452</v>
-      </c>
-      <c r="B23">
-        <v>23</v>
-      </c>
-      <c r="C23">
-        <v>72</v>
-      </c>
-      <c r="D23">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>45459</v>
-      </c>
-      <c r="B24">
-        <v>22</v>
-      </c>
-      <c r="C24">
-        <v>73</v>
-      </c>
-      <c r="D24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>45466</v>
-      </c>
-      <c r="B25">
-        <v>22</v>
-      </c>
-      <c r="C25">
-        <v>72</v>
-      </c>
-      <c r="D25">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
-        <v>45473</v>
-      </c>
-      <c r="B26">
-        <v>22</v>
-      </c>
-      <c r="C26">
-        <v>94</v>
-      </c>
-      <c r="D26">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
-        <v>45480</v>
-      </c>
-      <c r="B27">
-        <v>23</v>
-      </c>
-      <c r="C27">
-        <v>68</v>
-      </c>
-      <c r="D27">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
-        <v>45487</v>
-      </c>
-      <c r="B28">
-        <v>23</v>
-      </c>
-      <c r="C28">
-        <v>70</v>
-      </c>
-      <c r="D28">
-        <v>13</v>
+      <c r="B28" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.67</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
-        <v>45494</v>
-      </c>
-      <c r="B29">
-        <v>22</v>
-      </c>
-      <c r="C29">
-        <v>70</v>
-      </c>
-      <c r="D29">
-        <v>14</v>
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.65</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
-        <v>45501</v>
-      </c>
-      <c r="B30">
-        <v>21</v>
-      </c>
-      <c r="C30">
-        <v>69</v>
-      </c>
-      <c r="D30">
-        <v>13</v>
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.66</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
-        <v>45508</v>
-      </c>
-      <c r="B31">
-        <v>22</v>
-      </c>
-      <c r="C31">
-        <v>69</v>
-      </c>
-      <c r="D31">
-        <v>10</v>
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.69</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
-        <v>45515</v>
-      </c>
-      <c r="B32">
-        <v>23</v>
-      </c>
-      <c r="C32">
-        <v>69</v>
-      </c>
-      <c r="D32">
-        <v>10</v>
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.62</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
-        <v>45522</v>
-      </c>
-      <c r="B33">
-        <v>21</v>
-      </c>
-      <c r="C33">
-        <v>68</v>
-      </c>
-      <c r="D33">
-        <v>11</v>
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.66</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
-        <v>45529</v>
-      </c>
-      <c r="B34">
-        <v>22</v>
-      </c>
-      <c r="C34">
-        <v>68</v>
-      </c>
-      <c r="D34">
-        <v>10</v>
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.67</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
-        <v>45536</v>
-      </c>
-      <c r="B35">
-        <v>21</v>
-      </c>
-      <c r="C35">
-        <v>68</v>
-      </c>
-      <c r="D35">
-        <v>16</v>
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.7</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
-        <v>45543</v>
-      </c>
-      <c r="B36">
-        <v>19</v>
-      </c>
-      <c r="C36">
-        <v>63</v>
-      </c>
-      <c r="D36">
-        <v>12</v>
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.68</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
-        <v>45550</v>
-      </c>
-      <c r="B37">
-        <v>19</v>
-      </c>
-      <c r="C37">
-        <v>75</v>
-      </c>
-      <c r="D37">
-        <v>12</v>
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.68</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
-        <v>45557</v>
-      </c>
-      <c r="B38">
-        <v>20</v>
-      </c>
-      <c r="C38">
-        <v>60</v>
-      </c>
-      <c r="D38">
-        <v>12</v>
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.67</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
-        <v>45564</v>
-      </c>
-      <c r="B39">
-        <v>19</v>
-      </c>
-      <c r="C39">
-        <v>60</v>
-      </c>
-      <c r="D39">
-        <v>13</v>
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.68</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
-        <v>45571</v>
-      </c>
-      <c r="B40">
-        <v>20</v>
-      </c>
-      <c r="C40">
-        <v>62</v>
-      </c>
-      <c r="D40">
-        <v>13</v>
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.68</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
-        <v>45578</v>
-      </c>
-      <c r="B41">
-        <v>19</v>
-      </c>
-      <c r="C41">
-        <v>62</v>
-      </c>
-      <c r="D41">
-        <v>13</v>
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.67</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
-        <v>45585</v>
-      </c>
-      <c r="B42">
-        <v>19</v>
-      </c>
-      <c r="C42">
-        <v>63</v>
-      </c>
-      <c r="D42">
-        <v>15</v>
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.7</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
-        <v>45592</v>
-      </c>
-      <c r="B43">
-        <v>18</v>
-      </c>
-      <c r="C43">
-        <v>61</v>
-      </c>
-      <c r="D43">
-        <v>13</v>
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.68</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
-        <v>45599</v>
-      </c>
-      <c r="B44">
-        <v>17</v>
-      </c>
-      <c r="C44">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>53</v>
       </c>
-      <c r="D44">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
-        <v>45606</v>
-      </c>
-      <c r="B45">
-        <v>21</v>
-      </c>
-      <c r="C45">
-        <v>56</v>
-      </c>
-      <c r="D45">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
-        <v>45613</v>
-      </c>
-      <c r="B46">
-        <v>20</v>
-      </c>
-      <c r="C46">
-        <v>57</v>
-      </c>
-      <c r="D46">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
-        <v>45620</v>
-      </c>
-      <c r="B47">
-        <v>17</v>
-      </c>
-      <c r="C47">
-        <v>51</v>
-      </c>
-      <c r="D47">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
-        <v>45627</v>
-      </c>
-      <c r="B48">
-        <v>18</v>
-      </c>
-      <c r="C48">
-        <v>51</v>
-      </c>
-      <c r="D48">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
-        <v>45634</v>
-      </c>
-      <c r="B49">
-        <v>18</v>
-      </c>
-      <c r="C49">
+      <c r="B52" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>54</v>
       </c>
-      <c r="D49">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
-        <v>45641</v>
-      </c>
-      <c r="B50">
-        <v>17</v>
-      </c>
-      <c r="C50">
+      <c r="B53" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>55</v>
       </c>
-      <c r="D50">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
-        <v>45648</v>
-      </c>
-      <c r="B51">
-        <v>17</v>
-      </c>
-      <c r="C51">
-        <v>59</v>
-      </c>
-      <c r="D51">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
-        <v>45655</v>
-      </c>
-      <c r="B52">
-        <v>23</v>
-      </c>
-      <c r="C52">
-        <v>64</v>
-      </c>
-      <c r="D52">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
-        <v>45662</v>
-      </c>
-      <c r="B53">
-        <v>24</v>
-      </c>
-      <c r="C53">
-        <v>62</v>
-      </c>
-      <c r="D53">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
-        <v>45669</v>
-      </c>
-      <c r="B54">
-        <v>24</v>
-      </c>
-      <c r="C54">
-        <v>65</v>
-      </c>
-      <c r="D54">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
-        <v>45676</v>
-      </c>
-      <c r="B55">
-        <v>23</v>
-      </c>
-      <c r="C55">
-        <v>63</v>
-      </c>
-      <c r="D55">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
-        <v>45683</v>
-      </c>
-      <c r="B56">
-        <v>24</v>
-      </c>
-      <c r="C56">
-        <v>62</v>
-      </c>
-      <c r="D56">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
-        <v>45690</v>
-      </c>
-      <c r="B57">
-        <v>27</v>
-      </c>
-      <c r="C57">
-        <v>65</v>
-      </c>
-      <c r="D57">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
-        <v>45697</v>
-      </c>
-      <c r="B58">
-        <v>24</v>
-      </c>
-      <c r="C58">
-        <v>61</v>
-      </c>
-      <c r="D58">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
-        <v>45704</v>
-      </c>
-      <c r="B59">
-        <v>26</v>
-      </c>
-      <c r="C59">
-        <v>66</v>
-      </c>
-      <c r="D59">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
-        <v>45711</v>
-      </c>
-      <c r="B60">
-        <v>28</v>
-      </c>
-      <c r="C60">
-        <v>67</v>
-      </c>
-      <c r="D60">
-        <v>13</v>
+      <c r="B54" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>

--- a/week-01/Ex4A_GTrends.xlsx
+++ b/week-01/Ex4A_GTrends.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luise\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{161BDF74-6F1D-49FF-BAC6-1B500DF1D2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E3492654-8437-4637-9A6E-7906E55D72B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="3920" windowWidth="19200" windowHeight="11010" xr2:uid="{3F803DB3-4EA7-46F6-AE33-96C98E33509F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3F803DB3-4EA7-46F6-AE33-96C98E33509F}"/>
   </bookViews>
   <sheets>
     <sheet name="GTrends_milkshake_hamburger_202" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GTrends_milkshake_hamburger_202!$A$1:$E$52</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
-  <si>
-    <t>Category: All categories</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Region</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>District of Columbia</t>
+  </si>
+  <si>
+    <t># of regions</t>
+  </si>
+  <si>
+    <t>RegionID</t>
   </si>
 </sst>
 </file>
@@ -330,7 +336,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -508,6 +514,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -671,9 +683,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1049,743 +1062,965 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2568FC69-474F-4A0E-BC4E-D3E6E5AE3952}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="2">
+        <f>COUNTA(B2:B52)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="D16" s="1">
         <v>0.25</v>
       </c>
-      <c r="C4" s="1">
+      <c r="E16" s="1">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D4" s="1">
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="1">
         <v>0.61</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="D32" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C42" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D48" s="1">
         <v>0.24</v>
       </c>
-      <c r="C5" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.11</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="E48" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="1">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="D49" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="1">
         <v>0.66</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="D51" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E52" s="1">
         <v>0.13</v>
       </c>
-      <c r="D8" s="1">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0.11</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="D41" s="1">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D42" s="1">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C43" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D43" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D44" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C45" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="D46" s="1">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="C47" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C48" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D48" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D49" s="1">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D51" s="1">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.11</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D53" s="1">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="D54" s="1">
-        <v>0.66</v>
-      </c>
+      <c r="J52" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E52" xr:uid="{2568FC69-474F-4A0E-BC4E-D3E6E5AE3952}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E52">
+      <sortCondition ref="B1:B52"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>